--- a/docs/kofi-files/benchmarks-db/2026-pricing-benchmarks.xlsx
+++ b/docs/kofi-files/benchmarks-db/2026-pricing-benchmarks.xlsx
@@ -47,8 +47,8 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="00444444"/>
-      <sz val="9"/>
+      <color rgb="00555555"/>
+      <sz val="8.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -91,7 +91,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,17 +459,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Compiled Sep 19, 2026 · every band with its sources · estimates, not financial advice</t>
+          <t>Edition 1 · Compiled &amp; verified Sep 2026 · buyers get free quarterly refreshes · estimates, not financial advice</t>
         </is>
       </c>
     </row>
@@ -512,15 +515,20 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>What each source publishes (raw)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
@@ -557,15 +565,20 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
+          <t>HomeGuide $120–280 · Housecall Pro $120–280 · Thumbtack one-time $174–256</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
           <t>3 bed/2 bath typical ~$135–180, avg ~$180</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>HomeGuide; Housecall Pro; Thumbtack (one-time $174–256)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -595,15 +608,20 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
+          <t>Eufy $200–450 · Angi $180–375 · HomeGuide $230–600</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
           <t>First-time/seasonal; quote ~50% over standard</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Eufy; Angi; HomeGuide</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -633,15 +651,20 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
+          <t>HireAHelper $200–600 · HomeGuide $150–500 · Angi $120–420</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
           <t>Typical $250–450 for 3b2b</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>HireAHelper; HomeGuide; Angi</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -671,15 +694,20 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
+          <t>HomeGuide $25–75 · CottageCare $30–60 · LeadDuo $40–80</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
           <t>Use as floor check, quote flat by the job</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>HomeGuide; CottageCare</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -709,15 +737,20 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
           <t>Flat concrete at low end</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Pressure Washing guide</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -745,13 +778,18 @@
       <c r="E11" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Pressure Washing guide</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -781,15 +819,20 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
           <t>Delicate wood at top of range</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Pressure Washing guide</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -819,15 +862,20 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
           <t>Job minimum $150–200 typical</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Window Cleaning guide</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -857,15 +905,20 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
           <t>Job minimum $150–200 typical</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Window Cleaning guide</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -893,13 +946,18 @@
       <c r="E15" s="6" t="n">
         <v>1.75</v>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Angi $0.95–1.75 · CrewNest $1.00–1.50 · HomeGuide $0.75–2.00</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Angi; CrewNest calculator</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -927,13 +985,18 @@
       <c r="E16" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Angi $1.00–1.85 · CrewNest $1.50–2.25 · MyQuoteIQ $1.25–1.85</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Angi; CrewNest calculator</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -961,13 +1024,18 @@
       <c r="E17" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>CrewNest $2.25–3.50 · CleanPro $1.40–3.45</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>CrewNest; CleanPro Gutter Cleaning</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -997,15 +1065,20 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
+          <t>HomeGuide $100–275 · Modernize $128–320</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
           <t>Most homes carry 150–200 ft of gutter</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>HomeGuide; Modernize</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1035,15 +1108,20 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
           <t>Job minimum $100–150</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Junk Removal guide</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1071,13 +1149,18 @@
       <c r="E20" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Junk Removal guide</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1105,13 +1188,18 @@
       <c r="E21" s="6" t="n">
         <v>420</v>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Junk Removal guide</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1139,13 +1227,18 @@
       <c r="E22" s="6" t="n">
         <v>800</v>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Junk Removal guide</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1173,13 +1266,18 @@
       <c r="E23" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Post-Construction guide</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1207,13 +1305,18 @@
       <c r="E24" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Post-Construction guide</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1241,13 +1344,18 @@
       <c r="E25" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Post-Construction guide</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1284,15 +1392,20 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
+          <t>LawnLove $30–70 · CrewNest $35–75 · Thumbtack ~$35 · Jobber $25–75 · operator ~$30</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
           <t>LawnLove $30–70; CrewNest $35–75; Thumbtack ~$35; Jobber $25–75; Reddit ~$30</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>LawnLove; CrewNest; Thumbtack; Jobber; operator reports</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1322,15 +1435,20 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
+          <t>Thumbtack ~$40 · InvoiceFly $50–150 by length · LawnLove upper band</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
           <t>InvoiceFly up to $150 by length</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Thumbtack; InvoiceFly; LawnLove</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1360,15 +1478,20 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
+          <t>Thumbtack ~$60 (150 ft) · CrewNest to $75 · InvoiceFly to $150</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
           <t>Long/sloped can go higher</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Thumbtack; CrewNest; InvoiceFly</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1398,15 +1521,20 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
+          <t>InvoiceFly $350–700 · Angi $300–700</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
           <t>Angi $300–700; steep/large lots can exceed</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>InvoiceFly; Angi; LawnLove</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1436,15 +1564,20 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
+          <t>TaskRabbit ~$41 avg · Jobber $25–75 · LawnLove $25–75</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
           <t>TaskRabbit national avg ~$41</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>TaskRabbit; Jobber; LawnLove</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1474,15 +1607,20 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
+          <t>CrewNest $150–500+ · Angi $75–200 small-lot</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
           <t>Small-lot full service $75–200</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>CrewNest; Angi</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1519,15 +1657,20 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
+          <t>LawnSite operators $15–20 · HomeGuide/Angi whole-job $75–206</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
           <t>Contractors report $15–20</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>LawnStarter; Angi; LawnSite operator rates</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1557,15 +1700,20 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
+          <t>Operators $35–40 (standard seed) · Green Lawn Fertilizing ~$85 full-service</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>Standard seed rate ~3 lb/1,000 sq ft</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>HomeGuide; CountBricks; operator reports</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1595,15 +1743,20 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
           <t>Premium operator programs</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>CountBricks; operator rates</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -1631,13 +1784,18 @@
       <c r="E37" s="6" t="n">
         <v>185</v>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>LawnStarter 2026 table $115–185</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>LawnStarter (2026 table)</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1667,15 +1825,20 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
+          <t>LawnStarter $160–290 · Angi $200–500 (5–10k sq ft yards)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
           <t>Angi: 5,000–10,000 sq ft yards $200–500</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>LawnStarter; Angi</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1703,13 +1866,18 @@
       <c r="E39" s="6" t="n">
         <v>475</v>
       </c>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>LawnStarter 2026 table $230–475</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>LawnStarter (2026 table)</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1737,13 +1905,18 @@
       <c r="E40" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>LawnStarter $305+ (table); upper interpolated</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>LawnStarter (2026 table); interpolated top</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1771,13 +1944,18 @@
       <c r="E41" s="6" t="n">
         <v>925</v>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>LawnStarter 2026 table to $925</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>LawnStarter (2026 table)</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1807,15 +1985,20 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
+          <t>Angi ~$60 mid · LawnStarter $40–75 · GreenPal $75–150 w/ 2-hr min</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
           <t>2-hour minimum standard; late-season one-offs $250–400</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>Angi; LawnStarter; GreenPal</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1852,15 +2035,20 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
+          <t>Angi $1.50–3.50 · HomeAdvisor $1.50–3.50 · HomeGuide $1.50–3.50</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
           <t>Materials + labor; default 1 coat</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>Angi; HomeAdvisor; HomeGuide</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1888,13 +2076,18 @@
       <c r="E45" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Angi $20–50 · HomeAdvisor $30–60 · Costimates $20–50</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>Angi; HomeAdvisor; Costimates</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1924,15 +2117,20 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
+          <t>Angi $1.50–4.00 · HomeAdvisor $1.50–4.00 · HomeGuide $1.50–4.00</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
           <t>Prep (scraping, power wash) drives top end</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>Angi; HomeAdvisor; HomeGuide</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -1962,15 +2160,20 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
+          <t>Angi $40–75 · HomeAdvisor $30–60 · Costimates $50–60</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
           <t>Higher than interior (height, cleanup)</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>Angi; HomeAdvisor; Costimates</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -2000,15 +2203,20 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
+          <t>Interior $0.50–1.50 · Exterior $0.50–2.00 (Angi/HomeAdvisor)</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
           <t>Interior $0.50–1.50; exterior $0.50–2.00</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>Angi; HomeAdvisor</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -2045,15 +2253,20 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
           <t>Industry-standard band</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>Industry standard; MTB Food Cost guide</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -2081,13 +2294,18 @@
       <c r="E51" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>Industry standard; MTB Food Cost guide</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -2115,13 +2333,18 @@
       <c r="E52" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>Industry standard; MTB guides</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -2151,15 +2374,20 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
           <t>Average ~20%</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>Backbar; DoorDash; PuriMax</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -2187,13 +2415,18 @@
       <c r="E54" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>MAJC; Bevspot; Buyers Edge</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -2221,13 +2454,18 @@
       <c r="E55" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>MAJC; Restaurants Canada</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -2255,13 +2493,18 @@
       <c r="E56" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>MAJC; Buyers Edge</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>★★★ Multi-source verified</t>
         </is>
@@ -2289,13 +2532,18 @@
       <c r="E57" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Tip-Out guide</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>★★ Named sources / synthesis</t>
         </is>
@@ -2332,15 +2580,20 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
           <t>High-end markets exceed</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Booth Rent guide</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>★ Guideline</t>
         </is>
@@ -2370,15 +2623,20 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
           <t>Guideline ceiling before commission wins</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr">
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Booth Rent guide</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>★ Guideline</t>
         </is>
@@ -2408,15 +2666,20 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
           <t>Toward 60% with established book</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>Synthesis in MTB Booth Rent guide</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>★ Guideline</t>
         </is>
@@ -2453,15 +2716,20 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
           <t>100% markup = 50% margin (definition)</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Arithmetic rule</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>◆ Math rule</t>
         </is>
@@ -2491,15 +2759,20 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
           <t>At a 50% margin, ~+67% volume to break even on the discount</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>Arithmetic (discount math)</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>◆ Math rule</t>
         </is>
@@ -2507,13 +2780,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
